--- a/prototype-cs/doc-pm/线上客服排期_20260610.xlsx
+++ b/prototype-cs/doc-pm/线上客服排期_20260610.xlsx
@@ -2542,7 +2542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9042,7 +9042,7 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="14" t="inlineStr">
         <is>
-          <t>[(跳过-OMS已有工单)]  共 4 项 (本期不做)</t>
+          <t>[B8-工单系统(2期)]  共 6 项 (本期不做)</t>
         </is>
       </c>
     </row>
@@ -9062,10 +9062,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="D126" s="3" t="n"/>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>工单字段</t>
+        </is>
+      </c>
       <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="9" t="n"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>工单用于跨部门流转处理用户问题，支持标题、分类（售后/投诉/技术故障）、描述、附件、优先级、指派人配置。会话页、客户详情页均可为该客户创建工单。</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
           <t>无</t>
@@ -9073,22 +9085,22 @@
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>工单表单+分类体系</t>
         </is>
       </c>
       <c r="M126" s="10" t="inlineStr">
@@ -9113,10 +9125,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="D127" s="3" t="n"/>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>状态流转</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="9" t="n"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>工单状态流转：未分配→待处理→处理中→已解决→已关闭，支持流转记录留痕。</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
           <t>无</t>
@@ -9124,22 +9148,22 @@
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>5态状态机</t>
         </is>
       </c>
       <c r="M127" s="10" t="inlineStr">
@@ -9164,10 +9188,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="D128" s="3" t="n"/>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>工单操作</t>
+        </is>
+      </c>
       <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="9" t="n"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>支持接单、转单、回复、加抄送、状态变更，实现跨部门协作处理。</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
           <t>无</t>
@@ -9175,22 +9211,22 @@
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="K128" s="9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>接单/转单/抄送</t>
         </is>
       </c>
       <c r="M128" s="10" t="inlineStr">
@@ -9215,10 +9251,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="D129" s="3" t="n"/>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>与我相关</t>
+        </is>
+      </c>
       <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="9" t="n"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>提供「与我相关」筛选：待我处理、我创建的、抄送我的、我处理的、我解决的。</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
           <t>无</t>
@@ -9226,25 +9274,159 @@
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>5类筛选</t>
         </is>
       </c>
       <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="26" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>客服系统</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>商城运营后台(平台端)</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>工单系统</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>消息联动</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>自动生成</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>用户消息自动生成工单，实现会话与工单的关联追溯。（参考美团/饿了么）</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>B8-工单系统(2期)</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>消息自动生成工单</t>
+        </is>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="26" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>客服系统</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>商城运营后台(平台端)</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>工单系统</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>消息联动</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>一键生成</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>用户在会话框中的请求可一键生成工单，客服无需退出会话。（参考美团/饿了么）</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>B8-工单系统(2期)</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>会话一键生成工单</t>
+        </is>
+      </c>
+      <c r="M131" s="10" t="inlineStr">
         <is>
           <t>未分配(非本期)</t>
         </is>
@@ -9288,7 +9470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="13.7727272727273" customWidth="1" min="1" max="1"/>
@@ -10970,11 +11152,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>当前OMS有工单系统，可以先不做。不使用OMS的时候得开发。</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>工单字段</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>工单用于跨部门流转处理用户问题，支持标题、分类（售后/投诉/技术故障）、描述、附件、优先级、指派人配置。会话页、客户详情页均可为该客户创建工单。</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -10987,22 +11180,22 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>工单表单+分类体系</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
@@ -11027,11 +11220,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>当前OMS有工单系统，可以先不做。不使用OMS的时候得开发。</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>状态流转</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>工单状态流转：未分配→待处理→处理中→已解决→已关闭，支持流转记录留痕。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -11044,22 +11248,22 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>5态状态机</t>
         </is>
       </c>
       <c r="O26" s="10" t="inlineStr">
@@ -11084,11 +11288,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>当前OMS有工单系统，可以先不做。不使用OMS的时候得开发。</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>工单操作</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>支持接单、转单、回复、加抄送、状态变更，实现跨部门协作处理。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -11101,22 +11316,22 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>接单/转单/抄送</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr">
@@ -11141,11 +11356,22 @@
           <t>工单系统</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>当前OMS有工单系统，可以先不做。不使用OMS的时候得开发。</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>与我相关</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>提供「与我相关」筛选：待我处理、我创建的、抄送我的、我处理的、我解决的。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -11158,22 +11384,22 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>(跳过-OMS已有工单)</t>
+          <t>B8-工单系统(2期)</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>OMS有工单系统，先不做</t>
+          <t>5类筛选</t>
         </is>
       </c>
       <c r="O28" s="10" t="inlineStr">
@@ -11195,29 +11421,30 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>智能辅助</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>AI话术推荐</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>基于NLP实时推荐回复话术；检测到关键词时自动推送政策模板。(PPTX 3.5)</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
+          <t>工单系统</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>消息联动</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>自动生成</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>用户消息自动生成工单，实现会话与工单的关联追溯。（参考美团/饿了么）</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>2期-体验提升</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>后期需和业务确认需要什么数据</t>
-        </is>
-      </c>
+      <c r="H29" s="1" t="n"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -11225,27 +11452,27 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.5</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>B2-右栏AI辅助</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
+          <t>B8-工单系统(2期)</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M29" s="8" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>否(2期)</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>AI话术推荐</t>
+          <t>消息自动生成工单</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
@@ -11267,29 +11494,30 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>智能辅助</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>商品推荐</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>对话上下文识别购物意向，推荐关联商品并生成购买链接。(PPTX 3.5)</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
+          <t>工单系统</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>消息联动</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>一键生成</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>用户在会话框中的请求可一键生成工单，客服无需退出会话。（参考美团/饿了么）</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>2期-体验提升</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>后期需和业务确认需要什么数据</t>
-        </is>
-      </c>
+      <c r="H30" s="1" t="n"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -11297,27 +11525,27 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.5</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>B2-右栏AI辅助</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
+          <t>B8-工单系统(2期)</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>否(2期)</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>商品推荐</t>
+          <t>会话一键生成工单</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -11344,12 +11572,12 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>订单上下文提醒</t>
+          <t>AI话术推荐</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>自动识别用户订单号，推送对应订单的物流状态供客服一键回复。(PPTX 3.5)</t>
+          <t>基于NLP实时推荐回复话术；检测到关键词时自动推送政策模板。(PPTX 3.5)</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -11389,7 +11617,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>订单上下文提醒</t>
+          <t>AI话术推荐</t>
         </is>
       </c>
       <c r="O31" s="10" t="inlineStr">
@@ -11416,12 +11644,12 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>转人工意图提示</t>
+          <t>商品推荐</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>AI分析用户情绪异常(反复提问、负面关键词)，主动提示建议人工介入。(PPTX 3.5)</t>
+          <t>对话上下文识别购物意向，推荐关联商品并生成购买链接。(PPTX 3.5)</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -11461,7 +11689,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>转人工意图提示</t>
+          <t>商品推荐</t>
         </is>
       </c>
       <c r="O32" s="10" t="inlineStr">
@@ -11483,22 +11711,27 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>评价管理</t>
+          <t>智能辅助</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>客服评价</t>
+          <t>订单上下文提醒</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>查看用户对客服的评价详情和评分，支持按客服、时间、评分筛选。</t>
+          <t>自动识别用户订单号，推送对应订单的物流状态供客服一键回复。(PPTX 3.5)</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>后期需和业务确认需要什么数据</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -11508,12 +11741,12 @@
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 3.5</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>B6-评价管理</t>
+          <t>B2-右栏AI辅助</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -11521,19 +11754,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>评分详情+筛选</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>订单上下文提醒</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
         </is>
       </c>
     </row>
@@ -11550,17 +11783,17 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>数据监控</t>
+          <t>智能辅助</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>实时监控面板</t>
+          <t>转人工意图提示</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>当前在线客服数、排队数、平均响应时长、当前会话总数。(PPTX 3.6)</t>
+          <t>AI分析用户情绪异常(反复提问、负面关键词)，主动提示建议人工介入。(PPTX 3.5)</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -11580,12 +11813,12 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.6</t>
+          <t>✅ PPT 3.5</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>数据看板(2期)</t>
+          <t>B2-右栏AI辅助</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -11600,7 +11833,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>实时监控面板</t>
+          <t>转人工意图提示</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr">
@@ -11622,27 +11855,22 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>数据监控</t>
+          <t>评价管理</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>个人绩效看板</t>
+          <t>客服评价</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>今日接待量、平均响应时长、满意度、解决率。(PPTX 3.6)</t>
+          <t>查看用户对客服的评价详情和评分，支持按客服、时间、评分筛选。</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>2期-体验提升</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="inlineStr">
-        <is>
-          <t>后期需和业务确认需要什么数据</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
@@ -11652,12 +11880,12 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.6</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>数据看板(2期)</t>
+          <t>B6-评价管理</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -11665,19 +11893,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t>否(2期)</t>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>个人绩效看板</t>
-        </is>
-      </c>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>未分配(非本期)</t>
+          <t>评分详情+筛选</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -11699,12 +11927,12 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>预警机制</t>
+          <t>实时监控面板</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>响应时间超过阈值或满意度低于标准时自动通知主管。(PPTX 3.6)</t>
+          <t>当前在线客服数、排队数、平均响应时长、当前会话总数。(PPTX 3.6)</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -11732,9 +11960,9 @@
           <t>数据看板(2期)</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
@@ -11744,7 +11972,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>预警机制</t>
+          <t>实时监控面板</t>
         </is>
       </c>
       <c r="O36" s="10" t="inlineStr">
@@ -11766,17 +11994,17 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>统计报表</t>
+          <t>数据监控</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>会话量统计</t>
+          <t>个人绩效看板</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>按时间段统计会话总数、新会话数、已结束会话数，支持趋势图展示。</t>
+          <t>今日接待量、平均响应时长、满意度、解决率。(PPTX 3.6)</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -11796,7 +12024,7 @@
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 3.6</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -11816,7 +12044,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>会话量统计</t>
+          <t>个人绩效看板</t>
         </is>
       </c>
       <c r="O37" s="10" t="inlineStr">
@@ -11838,17 +12066,17 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>统计报表</t>
+          <t>数据监控</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>渠道统计</t>
+          <t>预警机制</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>各渠道（小程序、H5、PC）的会话量、转化率分布对比。</t>
+          <t>响应时间超过阈值或满意度低于标准时自动通知主管。(PPTX 3.6)</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -11868,7 +12096,7 @@
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 3.6</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -11876,9 +12104,9 @@
           <t>数据看板(2期)</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
@@ -11888,7 +12116,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>渠道统计</t>
+          <t>预警机制</t>
         </is>
       </c>
       <c r="O38" s="10" t="inlineStr">
@@ -11910,27 +12138,32 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>转人工</t>
+          <t>统计报表</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>关键词转人工</t>
+          <t>会话量统计</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>按时间段统计会话总数、新会话数、已结束会话数，支持趋势图展示。</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>自动检测</t>
+          <t>后期需和业务确认需要什么数据</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J39" s="1" t="inlineStr">
@@ -11940,27 +12173,27 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>B3-会话配置中心</t>
-        </is>
-      </c>
-      <c r="L39" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>数据看板(2期)</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>纯后端规则(仓库已有)</t>
-        </is>
-      </c>
-      <c r="O39" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>会话量统计</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
         </is>
       </c>
     </row>
@@ -11977,42 +12210,42 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>自动化配置</t>
+          <t>统计报表</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>欢迎语设置</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>可以自动设置什么类型的配置（对话配置页面）</t>
+          <t>渠道统计</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>配置用户进入会话时的自动欢迎语，支持按渠道和时段设置不同内容。</t>
+          <t>各渠道（小程序、H5、PC）的会话量、转化率分布对比。</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>后期需和业务确认需要什么数据</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>B3-会话配置中心</t>
+          <t>数据看板(2期)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -12020,19 +12253,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>欢迎语按渠道+时段(仓库已有)</t>
-        </is>
-      </c>
-      <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>渠道统计</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
         </is>
       </c>
     </row>
@@ -12049,17 +12282,12 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>自动化配置</t>
+          <t>转人工</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>离线自动回复</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>客服不在线时自动回复的配置，支持按时间段设置不同回复内容。</t>
+          <t>关键词转人工</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
@@ -12067,9 +12295,14 @@
           <t>1期-MVP</t>
         </is>
       </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>自动检测</t>
+        </is>
+      </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有</t>
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr">
@@ -12082,9 +12315,9 @@
           <t>B3-会话配置中心</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -12094,7 +12327,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>离线自动回复</t>
+          <t>纯后端规则(仓库已有)</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
@@ -12116,42 +12349,42 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>客服管理</t>
+          <t>自动化配置</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>客服账号管理</t>
+          <t>欢迎语设置</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>可以自动设置什么类型的配置（对话配置页面）</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>增删改查子账号，分配角色权限，支持部门分组。(PPTX 5.1)</t>
+          <t>配置用户进入会话时的自动欢迎语，支持按渠道和时段设置不同内容。</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>3期-AI智能化</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>未纳入讨论范围，待一期二期开发结束讨论</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有</t>
         </is>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.1</t>
+          <t>✅ PPT 2.2</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>B9-客服账号管理(3期)</t>
+          <t>B3-会话配置中心</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -12159,19 +12392,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>否(3期)</t>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>账号增删改查+角色权限</t>
-        </is>
-      </c>
-      <c r="O42" s="10" t="inlineStr">
-        <is>
-          <t>未分配(非本期)</t>
+          <t>欢迎语按渠道+时段(仓库已有)</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -12188,27 +12421,22 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>客服管理</t>
+          <t>自动化配置</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>分流设置(详细)</t>
+          <t>离线自动回复</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>新建技能组，按来源页面、商品SKU、订单状态等配置分流规则；为组内客服分配权重(0-10)。(PPTX 5.1)</t>
+          <t>客服不在线时自动回复的配置，支持按时间段设置不同回复内容。</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>3期-AI智能化</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>未纳入讨论范围，待一期二期开发结束讨论</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -12218,12 +12446,12 @@
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.1</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>B9-客服账号管理(3期)</t>
+          <t>B3-会话配置中心</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -12231,19 +12459,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>否(3期)</t>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>技能组+权重分流</t>
-        </is>
-      </c>
-      <c r="O43" s="10" t="inlineStr">
-        <is>
-          <t>未分配(非本期)</t>
+          <t>离线自动回复</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12493,12 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>默认客服组</t>
+          <t>客服账号管理</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>系统自动生成，承接未匹配分流规则的用户，不可删除。(PPTX 5.1)</t>
+          <t>增删改查子账号，分配角色权限，支持部门分组。(PPTX 5.1)</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -12298,9 +12526,9 @@
           <t>B9-客服账号管理(3期)</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
@@ -12310,7 +12538,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>默认客服组</t>
+          <t>账号增删改查+角色权限</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -12337,12 +12565,12 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>组间切换</t>
+          <t>分流设置(详细)</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>用户在某客服组未得到回复时，支持系统/客服手动将其切换到另一组。(PPTX 5.1)</t>
+          <t>新建技能组，按来源页面、商品SKU、订单状态等配置分流规则；为组内客服分配权重(0-10)。(PPTX 5.1)</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -12382,7 +12610,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>组间切换</t>
+          <t>技能组+权重分流</t>
         </is>
       </c>
       <c r="O45" s="10" t="inlineStr">
@@ -12409,12 +12637,12 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>离线留言管理(详细)</t>
+          <t>默认客服组</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>留言默认分配/指定客服分配/手动分配三种模式，支持留言列表批量处理。(PPTX 5.1)</t>
+          <t>系统自动生成，承接未匹配分流规则的用户，不可删除。(PPTX 5.1)</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -12442,9 +12670,9 @@
           <t>B9-客服账号管理(3期)</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
@@ -12454,7 +12682,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>离线留言管理(详细)</t>
+          <t>默认客服组</t>
         </is>
       </c>
       <c r="O46" s="10" t="inlineStr">
@@ -12476,17 +12704,17 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>渠道接入</t>
+          <t>客服管理</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>客服热线电话(IVR)</t>
+          <t>组间切换</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>支持客服热线电话接入，含IVR语音导航功能。(PPTX 5.2)</t>
+          <t>用户在某客服组未得到回复时，支持系统/客服手动将其切换到另一组。(PPTX 5.1)</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -12506,17 +12734,17 @@
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.2</t>
+          <t>✅ PPT 5.1</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>B10-渠道接入(3期)</t>
-        </is>
-      </c>
-      <c r="L47" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+          <t>B9-客服账号管理(3期)</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
@@ -12526,7 +12754,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>电话IVR接入</t>
+          <t>组间切换</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
@@ -12548,17 +12776,17 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>渠道接入</t>
+          <t>客服管理</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>邮件渠道</t>
+          <t>离线留言管理(详细)</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>支持邮件渠道接入客服系统。(PPTX 5.2)</t>
+          <t>留言默认分配/指定客服分配/手动分配三种模式，支持留言列表批量处理。(PPTX 5.1)</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -12578,17 +12806,17 @@
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.2</t>
+          <t>✅ PPT 5.1</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>B10-渠道接入(3期)</t>
-        </is>
-      </c>
-      <c r="L48" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+          <t>B9-客服账号管理(3期)</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
@@ -12598,7 +12826,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>邮件渠道</t>
+          <t>离线留言管理(详细)</t>
         </is>
       </c>
       <c r="O48" s="10" t="inlineStr">
@@ -12625,12 +12853,12 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>抖音/小红书私信</t>
+          <t>客服热线电话(IVR)</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>支持抖音、小红书等社交媒体私信渠道接入(如有入驻)。(PPTX 5.2)</t>
+          <t>支持客服热线电话接入，含IVR语音导航功能。(PPTX 5.2)</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -12670,7 +12898,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>抖音/小红书私信</t>
+          <t>电话IVR接入</t>
         </is>
       </c>
       <c r="O49" s="10" t="inlineStr">
@@ -12692,17 +12920,17 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>机器人配置</t>
+          <t>渠道接入</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>商品知识库</t>
+          <t>邮件渠道</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>自动同步商品SKU信息的知识库。(PPTX 5.3)</t>
+          <t>支持邮件渠道接入客服系统。(PPTX 5.2)</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
@@ -12722,17 +12950,17 @@
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.3</t>
+          <t>✅ PPT 5.2</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>B11-机器人配置(3期)</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+          <t>B10-渠道接入(3期)</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
@@ -12742,7 +12970,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>商品知识库</t>
+          <t>邮件渠道</t>
         </is>
       </c>
       <c r="O50" s="10" t="inlineStr">
@@ -12764,17 +12992,17 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>机器人配置</t>
+          <t>渠道接入</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>活动知识库</t>
+          <t>抖音/小红书私信</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>营销活动相关知识的维护管理。(PPTX 5.3)</t>
+          <t>支持抖音、小红书等社交媒体私信渠道接入(如有入驻)。(PPTX 5.2)</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
@@ -12794,17 +13022,17 @@
       </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.3</t>
+          <t>✅ PPT 5.2</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>B11-机器人配置(3期)</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+          <t>B10-渠道接入(3期)</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
@@ -12814,7 +13042,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>活动知识库</t>
+          <t>抖音/小红书私信</t>
         </is>
       </c>
       <c r="O51" s="10" t="inlineStr">
@@ -12841,12 +13069,12 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>物流/售后知识库</t>
+          <t>商品知识库</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>物流配送、售后服务相关知识的维护管理。(PPTX 5.3)</t>
+          <t>自动同步商品SKU信息的知识库。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -12886,7 +13114,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>物流/售后知识库</t>
+          <t>商品知识库</t>
         </is>
       </c>
       <c r="O52" s="10" t="inlineStr">
@@ -12913,12 +13141,12 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>转人工触发条件配置</t>
+          <t>活动知识库</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>配置关键词匹配、重复提问阈值等转人工触发条件。(PPTX 5.3)</t>
+          <t>营销活动相关知识的维护管理。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -12938,7 +13166,7 @@
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.3</t>
+          <t>✅ PPT 3.3</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -12958,7 +13186,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>转人工触发条件</t>
+          <t>活动知识库</t>
         </is>
       </c>
       <c r="O53" s="10" t="inlineStr">
@@ -12985,12 +13213,12 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>知识库匹配率监控</t>
+          <t>物流/售后知识库</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>知识库与意图匹配率监控、未解决Top问题统计。(PPTX 5.3)</t>
+          <t>物流配送、售后服务相关知识的维护管理。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -13030,7 +13258,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>匹配率监控</t>
+          <t>物流/售后知识库</t>
         </is>
       </c>
       <c r="O54" s="10" t="inlineStr">
@@ -13057,12 +13285,12 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>对话树可视化编辑</t>
+          <t>转人工触发条件配置</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>低代码/零代码配置平台，通过可视化拖拽组件实现业务流程构建。非技术人员可独立完成80%配置。(PPTX 5.3)</t>
+          <t>配置关键词匹配、重复提问阈值等转人工触发条件。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -13102,7 +13330,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>对话树可视化编辑</t>
+          <t>转人工触发条件</t>
         </is>
       </c>
       <c r="O55" s="10" t="inlineStr">
@@ -13124,17 +13352,17 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>数据报表</t>
+          <t>机器人配置</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>机器人报表</t>
+          <t>知识库匹配率监控</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>机器人应答率、转人工率、用户满意度、自助解决率、知识库命中率。(PPTX 5.4)</t>
+          <t>知识库与意图匹配率监控、未解决Top问题统计。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -13159,7 +13387,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>B11-数据报表(3期)</t>
+          <t>B11-机器人配置(3期)</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -13174,7 +13402,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>机器人报表</t>
+          <t>匹配率监控</t>
         </is>
       </c>
       <c r="O56" s="10" t="inlineStr">
@@ -13196,17 +13424,17 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>数据报表</t>
+          <t>机器人配置</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>服务质量报告</t>
+          <t>对话树可视化编辑</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>高频问题TOP10、人工未回复率占比、满意度星级分布、差评标签频次统计。(PPTX 5.4)</t>
+          <t>低代码/零代码配置平台，通过可视化拖拽组件实现业务流程构建。非技术人员可独立完成80%配置。(PPTX 5.3)</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
@@ -13226,12 +13454,12 @@
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.4</t>
+          <t>✅ PPT 5.3</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>B11-数据报表(3期)</t>
+          <t>B11-机器人配置(3期)</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -13246,7 +13474,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>服务质量报告</t>
+          <t>对话树可视化编辑</t>
         </is>
       </c>
       <c r="O57" s="10" t="inlineStr">
@@ -13273,12 +13501,12 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>工单报表</t>
+          <t>机器人报表</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>工单创建量、分类占比、平均处理时长、超时工单、各客服/部门处理数量。(PPTX 5.4)</t>
+          <t>机器人应答率、转人工率、用户满意度、自助解决率、知识库命中率。(PPTX 5.4)</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -13298,7 +13526,7 @@
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.4</t>
+          <t>✅ PPT 3.3</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -13318,7 +13546,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>工单报表</t>
+          <t>机器人报表</t>
         </is>
       </c>
       <c r="O58" s="10" t="inlineStr">
@@ -13345,12 +13573,12 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>客户分析</t>
+          <t>服务质量报告</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>咨询转化率、客服参与订单金额/数量、客诉率。(PPTX 5.4)</t>
+          <t>高频问题TOP10、人工未回复率占比、满意度星级分布、差评标签频次统计。(PPTX 5.4)</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
@@ -13390,7 +13618,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>客户分析</t>
+          <t>服务质量报告</t>
         </is>
       </c>
       <c r="O59" s="10" t="inlineStr">
@@ -13412,17 +13640,17 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>角色权限体系</t>
+          <t>数据报表</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>角色权限配置</t>
+          <t>工单报表</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>支持超级管理员、质检员、数据分析员、客服主管、普通客服、机器人训练师等6种角色。(PPTX 5.5)</t>
+          <t>工单创建量、分类占比、平均处理时长、超时工单、各客服/部门处理数量。(PPTX 5.4)</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -13442,12 +13670,12 @@
       </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 5.5</t>
+          <t>✅ PPT 5.4</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>B9-客服账号管理(3期)</t>
+          <t>B11-数据报表(3期)</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -13462,7 +13690,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>6种角色权限</t>
+          <t>工单报表</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
@@ -13484,17 +13712,17 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>智能客服-核心能力</t>
+          <t>数据报表</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>意图识别</t>
+          <t>客户分析</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>支持多轮对话上下文理解(5轮+)与跨场景意图识别；售前与售后场景自动切换。(PPTX 4.1)</t>
+          <t>咨询转化率、客服参与订单金额/数量、客诉率。(PPTX 5.4)</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
@@ -13514,17 +13742,17 @@
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.1</t>
+          <t>✅ PPT 5.4</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-核心能力(3期)</t>
-        </is>
-      </c>
-      <c r="L61" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+          <t>B11-数据报表(3期)</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
@@ -13534,7 +13762,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>意图识别</t>
+          <t>客户分析</t>
         </is>
       </c>
       <c r="O61" s="10" t="inlineStr">
@@ -13556,17 +13784,17 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>智能客服-核心能力</t>
+          <t>角色权限体系</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>知识图谱</t>
+          <t>角色权限配置</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>整合商品、订单、物流、售后策略数据，支持动态推理与回答生成。(PPTX 4.1)</t>
+          <t>支持超级管理员、质检员、数据分析员、客服主管、普通客服、机器人训练师等6种角色。(PPTX 5.5)</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
@@ -13586,17 +13814,17 @@
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.1</t>
+          <t>✅ PPT 5.5</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-核心能力(3期)</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+          <t>B9-客服账号管理(3期)</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
@@ -13606,7 +13834,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>知识图谱</t>
+          <t>6种角色权限</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
@@ -13633,12 +13861,12 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>NLP多模态</t>
+          <t>意图识别</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>支持文本+图片+语音多模态输入；用户上传商品图片后可自动识别并关联SKU、库存信息。(PPTX 4.1)</t>
+          <t>支持多轮对话上下文理解(5轮+)与跨场景意图识别；售前与售后场景自动切换。(PPTX 4.1)</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -13678,7 +13906,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>NLP多模态</t>
+          <t>意图识别</t>
         </is>
       </c>
       <c r="O63" s="10" t="inlineStr">
@@ -13705,12 +13933,12 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>文档解析</t>
+          <t>知识图谱</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>自动解析Excel/PDF/WORD格式的业务文档并结构化，无需手工配置新问答。(PPTX 4.1)</t>
+          <t>整合商品、订单、物流、售后策略数据，支持动态推理与回答生成。(PPTX 4.1)</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
@@ -13750,7 +13978,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>文档解析</t>
+          <t>知识图谱</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
@@ -13777,12 +14005,12 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>上下文记忆</t>
+          <t>NLP多模态</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>对话间保持上下文(如用户先问A商品，后续有红色的吗应理解针对A商品)。(PPTX 4.1)</t>
+          <t>支持文本+图片+语音多模态输入；用户上传商品图片后可自动识别并关联SKU、库存信息。(PPTX 4.1)</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
@@ -13822,7 +14050,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>上下文记忆</t>
+          <t>NLP多模态</t>
         </is>
       </c>
       <c r="O65" s="10" t="inlineStr">
@@ -13844,17 +14072,17 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>智能客服-售前场景</t>
+          <t>智能客服-核心能力</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>商品参数对比</t>
+          <t>文档解析</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>用户提出A和B哪个好时，机器人输出参数对比表格及结论。(PPTX 4.2)</t>
+          <t>自动解析Excel/PDF/WORD格式的业务文档并结构化，无需手工配置新问答。(PPTX 4.1)</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
@@ -13874,12 +14102,12 @@
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.2</t>
+          <t>✅ PPT 4.1</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-售前(3期)</t>
+          <t>B12-智能客服-核心能力(3期)</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
@@ -13894,7 +14122,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>商品参数对比</t>
+          <t>文档解析</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
@@ -13916,17 +14144,17 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>智能客服-售前场景</t>
+          <t>智能客服-核心能力</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>促销活动解读</t>
+          <t>上下文记忆</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>针对满减、折扣、优惠券规则进行清晰说明并计算示例。(PPTX 4.2)</t>
+          <t>对话间保持上下文(如用户先问A商品，后续有红色的吗应理解针对A商品)。(PPTX 4.1)</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
@@ -13946,12 +14174,12 @@
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.2</t>
+          <t>✅ PPT 4.1</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-售前(3期)</t>
+          <t>B12-智能客服-核心能力(3期)</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
@@ -13966,7 +14194,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>促销活动解读</t>
+          <t>上下文记忆</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
@@ -13993,12 +14221,12 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>尺码/规格推荐</t>
+          <t>商品参数对比</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>根据用户身高体重等数据推荐合适的服饰鞋靴尺码。(PPTX 4.2)</t>
+          <t>用户提出A和B哪个好时，机器人输出参数对比表格及结论。(PPTX 4.2)</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
@@ -14038,7 +14266,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>尺码/规格推荐</t>
+          <t>商品参数对比</t>
         </is>
       </c>
       <c r="O68" s="10" t="inlineStr">
@@ -14065,12 +14293,12 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>个性化商品推荐</t>
+          <t>促销活动解读</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>结合用户浏览记录、购买历史，精准推荐相关商品。(PPTX 4.2)</t>
+          <t>针对满减、折扣、优惠券规则进行清晰说明并计算示例。(PPTX 4.2)</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
@@ -14090,7 +14318,7 @@
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.5</t>
+          <t>✅ PPT 4.2</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -14110,7 +14338,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>个性化商品推荐</t>
+          <t>促销活动解读</t>
         </is>
       </c>
       <c r="O69" s="10" t="inlineStr">
@@ -14137,12 +14365,12 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>热点问题预测</t>
+          <t>尺码/规格推荐</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>根据用户输入实时内容预测可能想问的下一个问题，同步展示相关信息。(PPTX 4.2)</t>
+          <t>根据用户身高体重等数据推荐合适的服饰鞋靴尺码。(PPTX 4.2)</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
@@ -14182,7 +14410,7 @@
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>热点问题预测</t>
+          <t>尺码/规格推荐</t>
         </is>
       </c>
       <c r="O70" s="10" t="inlineStr">
@@ -14204,17 +14432,17 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>智能客服-售中售后</t>
+          <t>智能客服-售前场景</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>物流跟踪(机器人)</t>
+          <t>个性化商品推荐</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>实时查询物流轨迹，主动推送异常预警(如包裹滞留超过3天)。(PPTX 4.3)</t>
+          <t>结合用户浏览记录、购买历史，精准推荐相关商品。(PPTX 4.2)</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
@@ -14234,12 +14462,12 @@
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.3</t>
+          <t>✅ PPT 3.5</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-售中售后(3期)</t>
+          <t>B12-智能客服-售前(3期)</t>
         </is>
       </c>
       <c r="L71" s="11" t="inlineStr">
@@ -14254,7 +14482,7 @@
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>物流跟踪</t>
+          <t>个性化商品推荐</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
@@ -14276,17 +14504,17 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>智能客服-售中售后</t>
+          <t>智能客服-售前场景</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>订单状态查询(机器人)</t>
+          <t>热点问题预测</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>查询订单详情(支付状态、发货进度、预计送达时间)。(PPTX 4.3)</t>
+          <t>根据用户输入实时内容预测可能想问的下一个问题，同步展示相关信息。(PPTX 4.2)</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
@@ -14306,12 +14534,12 @@
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.3</t>
+          <t>✅ PPT 4.2</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>B12-智能客服-售中售后(3期)</t>
+          <t>B12-智能客服-售前(3期)</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
@@ -14326,7 +14554,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>订单状态查询</t>
+          <t>热点问题预测</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
@@ -14353,12 +14581,12 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>退换货引导(机器人)</t>
+          <t>物流跟踪(机器人)</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>引导用户自助发起退换货申请，填写原因并上传凭证。(PPTX 4.3)</t>
+          <t>实时查询物流轨迹，主动推送异常预警(如包裹滞留超过3天)。(PPTX 4.3)</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
@@ -14398,7 +14626,7 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>退换货引导</t>
+          <t>物流跟踪</t>
         </is>
       </c>
       <c r="O73" s="10" t="inlineStr">
@@ -14425,12 +14653,12 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>退差价/改地址(机器人)</t>
+          <t>订单状态查询(机器人)</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>支持对话内自助操作退差价、修改收货地址。(PPTX 4.3)</t>
+          <t>查询订单详情(支付状态、发货进度、预计送达时间)。(PPTX 4.3)</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
@@ -14470,7 +14698,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>退差价/改地址</t>
+          <t>订单状态查询</t>
         </is>
       </c>
       <c r="O74" s="10" t="inlineStr">
@@ -14497,12 +14725,12 @@
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>延期发货检测</t>
+          <t>退换货引导(机器人)</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>检测到订单即将超时，主动弹出提示并引导用户处理。(PPTX 4.3)</t>
+          <t>引导用户自助发起退换货申请，填写原因并上传凭证。(PPTX 4.3)</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
@@ -14542,7 +14770,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>延期发货检测</t>
+          <t>退换货引导</t>
         </is>
       </c>
       <c r="O75" s="10" t="inlineStr">
@@ -14564,17 +14792,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>人机协同机制</t>
+          <t>智能客服-售中售后</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>无缝转人工</t>
+          <t>退差价/改地址(机器人)</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>机器人无法解决时一键转人工，历史对话同步，用户无需重复表达。(PPTX 4.4)</t>
+          <t>支持对话内自助操作退差价、修改收货地址。(PPTX 4.3)</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
@@ -14594,17 +14822,17 @@
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.4</t>
+          <t>✅ PPT 4.3</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>B12-人机协同(3期)</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+          <t>B12-智能客服-售中售后(3期)</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
@@ -14614,7 +14842,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>无缝转人工</t>
+          <t>退差价/改地址</t>
         </is>
       </c>
       <c r="O76" s="10" t="inlineStr">
@@ -14636,17 +14864,17 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>人机协同机制</t>
+          <t>智能客服-售中售后</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>辅助模式</t>
+          <t>延期发货检测</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>机器人辅助客服输入话术，客服主导回复。(PPTX 4.4)</t>
+          <t>检测到订单即将超时，主动弹出提示并引导用户处理。(PPTX 4.3)</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
@@ -14666,17 +14894,17 @@
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 4.4</t>
+          <t>✅ PPT 4.3</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>B12-人机协同(3期)</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
+          <t>B12-智能客服-售中售后(3期)</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr">
@@ -14686,7 +14914,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>辅助模式</t>
+          <t>延期发货检测</t>
         </is>
       </c>
       <c r="O77" s="10" t="inlineStr">
@@ -14713,12 +14941,12 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>AI质检与会话摘要</t>
+          <t>无缝转人工</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>自动分析客服与用户的对话内容，生成标准化的会话摘要，供主管复盘及数据分析。(PPTX 4.4)</t>
+          <t>机器人无法解决时一键转人工，历史对话同步，用户无需重复表达。(PPTX 4.4)</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
@@ -14746,9 +14974,9 @@
           <t>B12-人机协同(3期)</t>
         </is>
       </c>
-      <c r="L78" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
@@ -14758,7 +14986,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>AI质检与会话摘要</t>
+          <t>无缝转人工</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -14775,27 +15003,32 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>前端商城（PC/H5/小程序）</t>
+          <t>商城运营后台(平台端)</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>客服入口</t>
+          <t>人机协同机制</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>在线客服</t>
+          <t>辅助模式</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>支持文字、表情、图片、语音消息收发；支持发送订单卡片、商品卡片，便于客服快速定位用户咨询的商品与订单上下文。</t>
+          <t>机器人辅助客服输入话术，客服主导回复。(PPTX 4.4)</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>3期-AI智能化</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>未纳入讨论范围，待一期二期开发结束讨论</t>
         </is>
       </c>
       <c r="I79" s="1" t="inlineStr">
@@ -14805,32 +15038,32 @@
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 4.4</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>C1-客服入口地图</t>
-        </is>
-      </c>
-      <c r="L79" s="12" t="inlineStr">
-        <is>
-          <t>前端UI</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>B12-人机协同(3期)</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>否(3期)</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>在线客服聊天入口</t>
-        </is>
-      </c>
-      <c r="O79" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>辅助模式</t>
+        </is>
+      </c>
+      <c r="O79" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
         </is>
       </c>
     </row>
@@ -14842,27 +15075,32 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>前端商城（PC/H5/小程序）</t>
+          <t>商城运营后台(平台端)</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>客服入口</t>
+          <t>人机协同机制</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>电话呼叫</t>
+          <t>AI质检与会话摘要</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>在商品页或客服对话页提供一键拨打客服电话图标，满足紧急或复杂问题的语音沟通需求。</t>
+          <t>自动分析客服与用户的对话内容，生成标准化的会话摘要，供主管复盘及数据分析。(PPTX 4.4)</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>3期-AI智能化</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>未纳入讨论范围，待一期二期开发结束讨论</t>
         </is>
       </c>
       <c r="I80" s="1" t="inlineStr">
@@ -14872,32 +15110,32 @@
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 4.4</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>C1-客服入口地图</t>
-        </is>
-      </c>
-      <c r="L80" s="12" t="inlineStr">
-        <is>
-          <t>前端UI</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>B12-人机协同(3期)</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="inlineStr">
+        <is>
+          <t>否(3期)</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>电话呼叫(H5)</t>
-        </is>
-      </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>AI质检与会话摘要</t>
+        </is>
+      </c>
+      <c r="O80" s="10" t="inlineStr">
+        <is>
+          <t>未分配(非本期)</t>
         </is>
       </c>
     </row>
@@ -14919,17 +15157,12 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>咨询入口</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>商品详情页</t>
+          <t>在线客服</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>在商品详情页底部或侧边提供在线咨询按钮，一键进入客服对话。</t>
+          <t>支持文字、表情、图片、语音消息收发；支持发送订单卡片、商品卡片，便于客服快速定位用户咨询的商品与订单上下文。</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
@@ -14944,7 +15177,7 @@
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.1</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -14964,7 +15197,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>商品详情页</t>
+          <t>在线客服聊天入口</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr">
@@ -14989,14 +15222,14 @@
           <t>客服入口</t>
         </is>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>订单详情页</t>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>电话呼叫</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>在订单详情页提供联系客服入口，自动关联当前订单信息。</t>
+          <t>在商品页或客服对话页提供一键拨打客服电话图标，满足紧急或复杂问题的语音沟通需求。</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
@@ -15011,7 +15244,7 @@
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.1</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -15031,7 +15264,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>订单详情页(带入订单)</t>
+          <t>电话呼叫(H5)</t>
         </is>
       </c>
       <c r="O82" s="6" t="inlineStr">
@@ -15056,14 +15289,19 @@
           <t>客服入口</t>
         </is>
       </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>咨询入口</t>
+        </is>
+      </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>个人中心/我的</t>
+          <t>商品详情页</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>在个人中心设置客服入口，方便用户随时找到客服。</t>
+          <t>在商品详情页底部或侧边提供在线咨询按钮，一键进入客服对话。</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
@@ -15098,7 +15336,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>个人中心</t>
+          <t>商品详情页</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr">
@@ -15123,19 +15361,14 @@
           <t>客服入口</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>咨询入口</t>
-        </is>
-      </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>购物车页</t>
+          <t>订单详情页</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>咨询购物车内商品相关问题，自动带入购物车商品信息。(PPTX 2.1)</t>
+          <t>在订单详情页提供联系客服入口，自动关联当前订单信息。</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
@@ -15170,7 +15403,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>购物车页(带入商品)</t>
+          <t>订单详情页(带入订单)</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr">
@@ -15197,12 +15430,12 @@
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>物流详情页（）</t>
+          <t>个人中心/我的</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>物流客服和在线客服</t>
+          <t>在个人中心设置客服入口，方便用户随时找到客服。</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
@@ -15237,7 +15470,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>物流详情页</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr">
@@ -15262,9 +15495,19 @@
           <t>客服入口</t>
         </is>
       </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>咨询入口</t>
+        </is>
+      </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>退换货入口</t>
+          <t>购物车页</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>咨询购物车内商品相关问题，自动带入购物车商品信息。(PPTX 2.1)</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
@@ -15299,7 +15542,7 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>退换货入口</t>
+          <t>购物车页(带入商品)</t>
         </is>
       </c>
       <c r="O86" s="6" t="inlineStr">
@@ -15324,14 +15567,14 @@
           <t>客服入口</t>
         </is>
       </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>全站悬浮窗（首页）</t>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>物流详情页（）</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>右下角悬浮客服入口，支持拖拽，方便用户随时发起咨询。(PPTX 2.1)</t>
+          <t>物流客服和在线客服</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
@@ -15341,7 +15584,7 @@
       </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J87" s="1" t="inlineStr">
@@ -15366,7 +15609,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>全站悬浮窗(仓库已有)</t>
+          <t>物流详情页</t>
         </is>
       </c>
       <c r="O87" s="6" t="inlineStr">
@@ -15388,57 +15631,52 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>会话体验</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>消息已读/未读</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>显示对方消息已读/未读状态，提升沟通体验。(PPTX 2.2)</t>
+          <t>客服入口</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>退换货入口</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>2期-体验提升</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>✅ PPT 2.1</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>C2-聊天窗主界面</t>
-        </is>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
-        </is>
-      </c>
-      <c r="M88" s="8" t="inlineStr">
-        <is>
-          <t>否(2期)</t>
+          <t>C1-客服入口地图</t>
+        </is>
+      </c>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>前端UI</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>已读未读(仓库已有)</t>
-        </is>
-      </c>
-      <c r="O88" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>退换货入口</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -15455,22 +15693,17 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>会话体验</t>
+          <t>客服入口</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>断线重连</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>咨询记录</t>
+          <t>全站悬浮窗（首页）</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>网络异常后自动重连并恢复历史会话，确保会话不丢失。(PPTX 2.2)</t>
+          <t>右下角悬浮客服入口，支持拖拽，方便用户随时发起咨询。(PPTX 2.1)</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
@@ -15485,17 +15718,17 @@
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>✅ PPT 2.1</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>C2-聊天窗主界面</t>
-        </is>
-      </c>
-      <c r="L89" s="11" t="inlineStr">
-        <is>
-          <t>后端逻辑</t>
+          <t>C1-客服入口地图</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>前端UI</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
@@ -15505,12 +15738,12 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>断线重连(仓库已有)</t>
-        </is>
-      </c>
-      <c r="O89" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>全站悬浮窗(仓库已有)</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -15527,27 +15760,27 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>FAQ机器人客服</t>
+          <t>会话体验</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>快捷问题</t>
+          <t>消息已读/未读</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>进入会话前展示常见问题快捷入口，客户可一键选择常见问题减少输入成本。</t>
+          <t>显示对方消息已读/未读状态，提升沟通体验。(PPTX 2.2)</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
         </is>
       </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有</t>
         </is>
       </c>
       <c r="J90" s="1" t="inlineStr">
@@ -15557,7 +15790,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>C3-FAQ机器人</t>
+          <t>C2-聊天窗主界面</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -15565,19 +15798,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>快捷问题入口</t>
-        </is>
-      </c>
-      <c r="O90" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>已读未读(仓库已有)</t>
+        </is>
+      </c>
+      <c r="O90" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -15594,57 +15827,62 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>FAQ机器人客服</t>
+          <t>会话体验</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>多轮引导</t>
+          <t>断线重连</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>咨询记录</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>机器人通过多轮问答逐步收集客户问题信息（如订单号、问题类型），引导至精准解决方案。</t>
+          <t>网络异常后自动重连并恢复历史会话，确保会话不丢失。(PPTX 2.2)</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>2期-体验提升</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>有</t>
         </is>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 2.2</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>C3-FAQ机器人</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>前后端联动</t>
-        </is>
-      </c>
-      <c r="M91" s="8" t="inlineStr">
-        <is>
-          <t>否(2期)</t>
+          <t>C2-聊天窗主界面</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>后端逻辑</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>多轮引导</t>
-        </is>
-      </c>
-      <c r="O91" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>断线重连(仓库已有)</t>
+        </is>
+      </c>
+      <c r="O91" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -15666,12 +15904,12 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>服务指南</t>
+          <t>快捷问题</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>提供退换货流程、支付方式、配送说明、发票政策等图文操作指南，引导客户自助解决问题。</t>
+          <t>进入会话前展示常见问题快捷入口，客户可一键选择常见问题减少输入成本。</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
@@ -15686,7 +15924,7 @@
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 2.2</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -15706,7 +15944,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>服务指南(图文)</t>
+          <t>快捷问题入口</t>
         </is>
       </c>
       <c r="O92" s="6" t="inlineStr">
@@ -15733,12 +15971,12 @@
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>智能自助服务</t>
+          <t>多轮引导</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>接入机器人客服，提供关注自动回复、关键词自动回复、常见问题FAQ指引，实现7x24小时秒级响应。</t>
+          <t>机器人通过多轮问答逐步收集客户问题信息（如订单号、问题类型），引导至精准解决方案。</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
@@ -15753,7 +15991,7 @@
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.3</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
@@ -15773,7 +16011,7 @@
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>智能自助服务</t>
+          <t>多轮引导</t>
         </is>
       </c>
       <c r="O93" s="6" t="inlineStr">
@@ -15795,22 +16033,22 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>智能自助服务</t>
+          <t>FAQ机器人客服</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>猜你想问</t>
+          <t>服务指南</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>基于用户当前浏览的商品和订单状态，预判可能的问题并主动推送。(PPTX 2.3)</t>
+          <t>提供退换货流程、支付方式、配送说明、发票政策等图文操作指南，引导客户自助解决问题。</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>2期-体验提升</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I94" s="1" t="inlineStr">
@@ -15820,7 +16058,7 @@
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.3</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -15833,14 +16071,14 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M94" s="8" t="inlineStr">
-        <is>
-          <t>否(2期)</t>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>猜你想问</t>
+          <t>服务指南(图文)</t>
         </is>
       </c>
       <c r="O94" s="6" t="inlineStr">
@@ -15862,22 +16100,17 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
+          <t>FAQ机器人客服</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
           <t>智能自助服务</t>
         </is>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>自助办理</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>对话框上方卡片</t>
-        </is>
-      </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>在对话窗内直连业务系统，支持自助查订单、改地址、退差价、申请退款等操作。(PPTX 2.3)</t>
+          <t>接入机器人客服，提供关注自动回复、关键词自动回复、常见问题FAQ指引，实现7x24小时秒级响应。</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
@@ -15912,7 +16145,7 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>自助办理(对接业务系统)</t>
+          <t>智能自助服务</t>
         </is>
       </c>
       <c r="O95" s="6" t="inlineStr">
@@ -15934,17 +16167,17 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>人工客服</t>
+          <t>智能自助服务</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>排队等待提示</t>
+          <t>猜你想问</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>转人工后展示当前排队人数与预计等待时间，支持留言选项避免长时间等待。</t>
+          <t>基于用户当前浏览的商品和订单状态，预判可能的问题并主动推送。(PPTX 2.3)</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
@@ -15959,12 +16192,12 @@
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>✅ PPT 2.3</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>C4-人工客服交互</t>
+          <t>C3-FAQ机器人</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -15979,12 +16212,12 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>排队等待提示</t>
-        </is>
-      </c>
-      <c r="O96" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>猜你想问</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -16001,22 +16234,27 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>人工客服</t>
+          <t>智能自助服务</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>留言与离线反馈</t>
+          <t>自助办理</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>对话框上方卡片</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>客服不在线时支持用户留言提交，并保留历史聊天记录，方便用户随时查看进度。</t>
+          <t>在对话窗内直连业务系统，支持自助查订单、改地址、退差价、申请退款等操作。(PPTX 2.3)</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
         </is>
       </c>
       <c r="I97" s="1" t="inlineStr">
@@ -16026,12 +16264,12 @@
       </c>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>✅ PPT 2.3</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>C4-人工客服交互</t>
+          <t>C3-FAQ机器人</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -16039,19 +16277,19 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M97" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>留言提交表单</t>
-        </is>
-      </c>
-      <c r="O97" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>自助办理(对接业务系统)</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -16073,17 +16311,17 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>服务评价</t>
+          <t>排队等待提示</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>会话结束后，用户可对本次客服的服务态度与专业性进行星级评价或文字反馈。</t>
+          <t>转人工后展示当前排队人数与预计等待时间，支持留言选项避免长时间等待。</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
+          <t>2期-体验提升</t>
         </is>
       </c>
       <c r="I98" s="1" t="inlineStr">
@@ -16106,14 +16344,14 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M98" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>服务评价弹窗</t>
+          <t>排队等待提示</t>
         </is>
       </c>
       <c r="O98" s="7" t="inlineStr">
@@ -16140,17 +16378,17 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>输入状态提示</t>
+          <t>留言与离线反馈</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>客服正在输入时，用户端显示客服正在输入提示，增强沟通体验。</t>
+          <t>客服不在线时支持用户留言提交，并保留历史聊天记录，方便用户随时查看进度。</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>2期-体验提升</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I99" s="1" t="inlineStr">
@@ -16160,12 +16398,12 @@
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 2.2</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>C2-聊天窗主界面</t>
+          <t>C4-人工客服交互</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -16173,14 +16411,14 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M99" s="8" t="inlineStr">
-        <is>
-          <t>否(2期)</t>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>输入状态提示</t>
+          <t>留言提交表单</t>
         </is>
       </c>
       <c r="O99" s="7" t="inlineStr">
@@ -16202,27 +16440,22 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>消息与交互</t>
+          <t>人工客服</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>订单卡片交互</t>
+          <t>服务评价</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>展示订单卡片，包含订单号、商品、金额、状态，客户可直接点击查看详情或执行操作。</t>
+          <t>会话结束后，用户可对本次客服的服务态度与专业性进行星级评价或文字反馈。</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP/2期-体验提升</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>可以选择订单进行操作（申请退换货、取消订单、修改地址）</t>
+          <t>1期-MVP</t>
         </is>
       </c>
       <c r="I100" s="1" t="inlineStr">
@@ -16232,12 +16465,12 @@
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t>❌ PPT未提及</t>
+          <t>✅ PPT 2.2</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>C2-聊天窗主界面</t>
+          <t>C4-人工客服交互</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -16252,7 +16485,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>★订单卡片(含退换货操作)</t>
+          <t>服务评价弹窗</t>
         </is>
       </c>
       <c r="O100" s="7" t="inlineStr">
@@ -16274,22 +16507,22 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>消息与交互</t>
+          <t>人工客服</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>商品卡片交互</t>
+          <t>输入状态提示</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>展示商品卡片，包含图片、名称、价格，客户可直接点击查看商品详情或加入购物车。</t>
+          <t>客服正在输入时，用户端显示客服正在输入提示，增强沟通体验。</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP/2期-体验提升</t>
+          <t>2期-体验提升</t>
         </is>
       </c>
       <c r="I101" s="1" t="inlineStr">
@@ -16299,7 +16532,7 @@
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.1</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
@@ -16312,14 +16545,14 @@
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="M101" s="8" t="inlineStr">
+        <is>
+          <t>否(2期)</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
         <is>
-          <t>★商品卡片(含加购)</t>
+          <t>输入状态提示</t>
         </is>
       </c>
       <c r="O101" s="7" t="inlineStr">
@@ -16346,12 +16579,12 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>富媒体消息</t>
+          <t>订单卡片交互</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>支持图文消息（一期）、视频消息、优惠券卡片等多种富媒体内容展示。</t>
+          <t>展示订单卡片，包含订单号、商品、金额、状态，客户可直接点击查看详情或执行操作。</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
@@ -16359,6 +16592,11 @@
           <t>1期-MVP/2期-体验提升</t>
         </is>
       </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>可以选择订单进行操作（申请退换货、取消订单、修改地址）</t>
+        </is>
+      </c>
       <c r="I102" s="1" t="inlineStr">
         <is>
           <t>无</t>
@@ -16366,7 +16604,7 @@
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 2.2</t>
+          <t>❌ PPT未提及</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
@@ -16386,7 +16624,7 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>★富媒体消息(图文/视频/券)</t>
+          <t>★订单卡片(含退换货操作)</t>
         </is>
       </c>
       <c r="O102" s="7" t="inlineStr">
@@ -16408,32 +16646,32 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>会话管理</t>
+          <t>消息与交互</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>历史会话</t>
+          <t>商品卡片交互</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>展示商品卡片，包含图片、名称、价格，客户可直接点击查看商品详情或加入购物车。</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>1期-MVP</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>一个聊天框保存所有聊天记录</t>
+          <t>1期-MVP/2期-体验提升</t>
         </is>
       </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>✅ PPT 3.7</t>
+          <t>✅ PPT 2.1</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
@@ -16453,7 +16691,7 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>历史会话(仓库已有)</t>
+          <t>★商品卡片(含加购)</t>
         </is>
       </c>
       <c r="O103" s="7" t="inlineStr">
@@ -16475,50 +16713,184 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
+          <t>消息与交互</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>富媒体消息</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>支持图文消息（一期）、视频消息、优惠券卡片等多种富媒体内容展示。</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>1期-MVP/2期-体验提升</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J104" s="1" t="inlineStr">
+        <is>
+          <t>✅ PPT 2.2</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>C2-聊天窗主界面</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>★富媒体消息(图文/视频/券)</t>
+        </is>
+      </c>
+      <c r="O104" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>客服系统</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>前端商城（PC/H5/小程序）</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>会话管理</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>历史会话</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>1期-MVP</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>一个聊天框保存所有聊天记录</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="J105" s="1" t="inlineStr">
+        <is>
+          <t>✅ PPT 3.7</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>C2-聊天窗主界面</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>前后端联动</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>历史会话(仓库已有)</t>
+        </is>
+      </c>
+      <c r="O105" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>客服系统</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>前端商城（PC/H5/小程序）</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
           <t>智能客服</t>
         </is>
       </c>
-      <c r="D104" s="1" t="inlineStr">
+      <c r="D106" s="1" t="inlineStr">
         <is>
           <t>基于大模型的智能客服-基础版</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>2期-体验提升</t>
         </is>
       </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="inlineStr">
         <is>
           <t>❌ PPT未提及</t>
         </is>
       </c>
-      <c r="K104" s="3" t="inlineStr">
+      <c r="K106" s="3" t="inlineStr">
         <is>
           <t>C3-FAQ机器人/C6(2期)</t>
         </is>
       </c>
-      <c r="L104" s="4" t="inlineStr">
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>前后端联动</t>
         </is>
       </c>
-      <c r="M104" s="8" t="inlineStr">
+      <c r="M106" s="8" t="inlineStr">
         <is>
           <t>否(2期)</t>
         </is>
       </c>
-      <c r="N104" s="3" t="inlineStr">
+      <c r="N106" s="3" t="inlineStr">
         <is>
           <t>大模型智能客服</t>
         </is>
       </c>
-      <c r="O104" s="6" t="inlineStr">
+      <c r="O106" s="6" t="inlineStr">
         <is>
           <t>A(部分)</t>
         </is>
